--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,116 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128326512</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101779</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Artrik vägkant, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>441887</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7058088</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>NorraInneslänt (IS)Erik Borgström</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128326512</v>
       </c>
       <c r="B3" t="n">
-        <v>101779</v>
+        <v>101784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128326512</v>
       </c>
       <c r="B3" t="n">
-        <v>101784</v>
+        <v>101877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128326512</v>
       </c>
       <c r="B3" t="n">
-        <v>101877</v>
+        <v>101893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128326512</v>
       </c>
       <c r="B3" t="n">
-        <v>101893</v>
+        <v>101898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128326512</v>
       </c>
       <c r="B3" t="n">
-        <v>101898</v>
+        <v>101904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128326512</v>
       </c>
       <c r="B3" t="n">
-        <v>101904</v>
+        <v>101905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128326512</v>
       </c>
       <c r="B3" t="n">
-        <v>101905</v>
+        <v>101932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128326512</v>
       </c>
       <c r="B3" t="n">
-        <v>101932</v>
+        <v>101945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>128326512</v>
       </c>
       <c r="B3" t="n">
-        <v>101945</v>
+        <v>101949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130177878</v>
       </c>
       <c r="B4" t="n">
-        <v>102147</v>
+        <v>102149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130177878</v>
       </c>
       <c r="B4" t="n">
-        <v>102149</v>
+        <v>102236</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130177878</v>
       </c>
       <c r="B4" t="n">
-        <v>102236</v>
+        <v>102239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130177878</v>
       </c>
       <c r="B4" t="n">
-        <v>102239</v>
+        <v>102265</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130177878</v>
       </c>
       <c r="B4" t="n">
-        <v>102265</v>
+        <v>102266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130177878</v>
       </c>
       <c r="B4" t="n">
-        <v>102266</v>
+        <v>102267</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>130177878</v>
       </c>
       <c r="B4" t="n">
-        <v>102267</v>
+        <v>102269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 13485-2025 artfynd.xlsx
+++ b/artfynd/A 13485-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>121520770</v>
       </c>
       <c r="B2" t="n">
-        <v>101502</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +775,7 @@
         <v>128326512</v>
       </c>
       <c r="B3" t="n">
-        <v>101949</v>
+        <v>102464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +885,7 @@
         <v>130177878</v>
       </c>
       <c r="B4" t="n">
-        <v>102269</v>
+        <v>102463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
